--- a/NOVEMBER/NOVEMBER KITCHEN OUTSTANDING/NOVEMBER BAYU AGNI MERTA (GAS) OUTSTANDING.xlsx
+++ b/NOVEMBER/NOVEMBER KITCHEN OUTSTANDING/NOVEMBER BAYU AGNI MERTA (GAS) OUTSTANDING.xlsx
@@ -27,38 +27,11 @@
 </file>
 
 <file path=xl/cellimages.xml><?xml version="1.0" encoding="utf-8"?>
-<etc:cellImages xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="ID_54351053BC8E46418B4A98193A9A278C" descr="WhatsApp Image 2025-11-17 at 10.35.18_bea5cd8c"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:srcRect l="2654" t="18293" r="2800" b="15108"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5393055" y="879475"/>
-          <a:ext cx="2617470" cy="3223895"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-</etc:cellImages>
+<etc:cellImages xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData"/>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
   <si>
     <t>DATE</t>
   </si>
@@ -81,10 +54,13 @@
     <t>TOTAL</t>
   </si>
   <si>
-    <t>0505</t>
+    <t>0503</t>
   </si>
   <si>
     <t>LPG 50KG</t>
+  </si>
+  <si>
+    <t>0505</t>
   </si>
 </sst>
 </file>
@@ -782,16 +758,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -801,13 +774,13 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1092,6 +1065,88 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>26035</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>26035</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2292350</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>2816860</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="ID_54351053BC8E46418B4A98193A9A278C" descr="WhatsApp Image 2025-11-17 at 10.35.18_bea5cd8c"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:srcRect l="2654" t="18293" r="2800" b="15108"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4930140" y="3150235"/>
+          <a:ext cx="2266315" cy="2790825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>38735</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>26035</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2279015</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>2817495</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="ID_505F3AF03F5A4CE89F8B74B2D8A60C1A" descr="WhatsApp Image 2025-12-04 at 17.32.54_d7b78ee3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4942840" y="305435"/>
+          <a:ext cx="2240280" cy="2791460"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1352,87 +1407,106 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="2" outlineLevelCol="6"/>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="3" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="10.8571428571429" style="2"/>
-    <col min="2" max="2" width="17.1428571428571" style="2" customWidth="1"/>
-    <col min="3" max="3" width="25.8571428571429" style="2" customWidth="1"/>
-    <col min="4" max="4" width="19.6952380952381" style="2" customWidth="1"/>
-    <col min="5" max="5" width="34.7238095238095" style="2" customWidth="1"/>
-    <col min="6" max="6" width="20.9333333333333" style="2" customWidth="1"/>
-    <col min="7" max="7" width="24.8761904761905" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.14285714285714" style="2"/>
+    <col min="1" max="1" width="10.8571428571429"/>
+    <col min="2" max="2" width="17.1428571428571" customWidth="1"/>
+    <col min="3" max="3" width="25.8571428571429" customWidth="1"/>
+    <col min="4" max="4" width="19.6952380952381" customWidth="1"/>
+    <col min="5" max="5" width="34.7238095238095" customWidth="1"/>
+    <col min="6" max="6" width="20.9333333333333" customWidth="1"/>
+    <col min="7" max="7" width="24.8761904761905" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="22" customHeight="1" spans="1:7">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="224" spans="1:7">
-      <c r="A2" s="4">
+    <row r="2" customFormat="1" ht="224" customHeight="1" spans="1:7">
+      <c r="A2" s="3">
+        <v>45975</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="6">
+        <v>2</v>
+      </c>
+      <c r="E2" s="5"/>
+      <c r="F2" s="7">
+        <v>975000</v>
+      </c>
+      <c r="G2" s="7">
+        <f>SUM(D2*F2)</f>
+        <v>1950000</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" ht="224" customHeight="1" spans="1:7">
+      <c r="A3" s="3">
         <v>45976</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="6" t="s">
+      <c r="B3" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D3" s="6">
         <v>4</v>
       </c>
-      <c r="E2" s="6" t="str">
-        <f>_xlfn.DISPIMG("ID_54351053BC8E46418B4A98193A9A278C",1)</f>
-        <v>=DISPIMG("ID_54351053BC8E46418B4A98193A9A278C",1)</v>
-      </c>
-      <c r="F2" s="8">
+      <c r="E3" s="5"/>
+      <c r="F3" s="7">
         <v>975000</v>
       </c>
-      <c r="G2" s="8">
-        <f>SUM(D2*F2)</f>
+      <c r="G3" s="7">
+        <f>SUM(D3*F3)</f>
         <v>3900000</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="23.25" spans="1:7">
-      <c r="A3" s="9" t="s">
+    <row r="4" customFormat="1" ht="23.25" spans="1:7">
+      <c r="A4" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="10">
-        <f>SUM(G2:G2)</f>
-        <v>3900000</v>
-      </c>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="9">
+        <f>SUM(G2:G3)</f>
+        <v>5850000</v>
+      </c>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="E4:G4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>